--- a/partial/sliding_window_results_window_7.xlsx
+++ b/partial/sliding_window_results_window_7.xlsx
@@ -463,13 +463,13 @@
         <v>29.75</v>
       </c>
       <c r="C2" t="n">
-        <v>29.55206922625512</v>
+        <v>29.58759074234123</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1979307737448792</v>
+        <v>-0.1624092576587692</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03917659119524657</v>
+        <v>0.02637676697327249</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.84</v>
       </c>
       <c r="C3" t="n">
-        <v>30.47912178875446</v>
+        <v>30.18283030166088</v>
       </c>
       <c r="D3" t="n">
-        <v>0.639121788754462</v>
+        <v>0.3428303016608787</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4084766608607032</v>
+        <v>0.1175326157368891</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.81</v>
       </c>
       <c r="C4" t="n">
-        <v>30.33429754739949</v>
+        <v>30.05240729647354</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5242975473994882</v>
+        <v>0.2424072964735444</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2748879182091186</v>
+        <v>0.05876129738361286</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.92</v>
       </c>
       <c r="C5" t="n">
-        <v>30.15789938435594</v>
+        <v>29.8008296316535</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2378993843559414</v>
+        <v>-0.1191703683464986</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05659611707693592</v>
+        <v>0.01420157669184016</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.98</v>
       </c>
       <c r="C6" t="n">
-        <v>29.56797042230956</v>
+        <v>29.81086508372359</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4120295776904364</v>
+        <v>-0.1691349162764055</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1697683728917593</v>
+        <v>0.02860661990382671</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.04</v>
       </c>
       <c r="C7" t="n">
-        <v>29.87083641622381</v>
+        <v>29.8588191652655</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1691635837761893</v>
+        <v>-0.1811808347345014</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02861631807600383</v>
+        <v>0.03282649487509071</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.21</v>
       </c>
       <c r="C8" t="n">
-        <v>29.50938272688767</v>
+        <v>29.96757500962112</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7006172731123357</v>
+        <v>-0.2424249903788791</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4908645633833651</v>
+        <v>0.05876987596019963</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.22</v>
       </c>
       <c r="C9" t="n">
-        <v>29.90408689872561</v>
+        <v>30.10526514425146</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3159131012743934</v>
+        <v>-0.1147348557485373</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09980108755680515</v>
+        <v>0.01316408712363765</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.38</v>
       </c>
       <c r="C10" t="n">
-        <v>29.81726096736508</v>
+        <v>30.16667345311208</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5627390326349229</v>
+        <v>-0.2133265468879237</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3166752188508888</v>
+        <v>0.04550821560712553</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.44</v>
       </c>
       <c r="C11" t="n">
-        <v>30.47190847918474</v>
+        <v>30.45523101141733</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03190847918473594</v>
+        <v>0.01523101141732397</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001018151043882727</v>
+        <v>0.0002319837087946531</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.48</v>
       </c>
       <c r="C12" t="n">
-        <v>30.34180917565251</v>
+        <v>30.47076606092922</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1381908243474932</v>
+        <v>-0.009233939070778518</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01909670393383972</v>
+        <v>8.526563076285005e-05</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.69</v>
       </c>
       <c r="C13" t="n">
-        <v>30.54504415376866</v>
+        <v>30.43801446389514</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1449558462313441</v>
+        <v>-0.2519855361048577</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02101219735664506</v>
+        <v>0.06349671040605256</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.75</v>
       </c>
       <c r="C14" t="n">
-        <v>30.37535326122348</v>
+        <v>30.69975840814894</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3746467387765229</v>
+        <v>-0.05024159185105859</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1403601788758842</v>
+        <v>0.002524217551728357</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.94</v>
       </c>
       <c r="C15" t="n">
-        <v>30.63839908210787</v>
+        <v>30.82994133128413</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3016009178921308</v>
+        <v>-0.1100586687158724</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09096311367337585</v>
+        <v>0.01211291055951016</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.95</v>
       </c>
       <c r="C16" t="n">
-        <v>30.85683821619653</v>
+        <v>30.96543978898074</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0931617838034704</v>
+        <v>0.01543978898073917</v>
       </c>
       <c r="E16" t="n">
-        <v>0.008679117961444559</v>
+        <v>0.0002383870837697546</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.02</v>
       </c>
       <c r="C17" t="n">
-        <v>31.42282016144514</v>
+        <v>31.14081628343929</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4028201614451419</v>
+        <v>0.120816283439293</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1622640824666902</v>
+        <v>0.01459657434408357</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.12</v>
       </c>
       <c r="C18" t="n">
-        <v>31.74538832666033</v>
+        <v>31.21232837632543</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6253883266603246</v>
+        <v>0.09232837632543323</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3911105591230009</v>
+        <v>0.008524529074890819</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.28</v>
       </c>
       <c r="C19" t="n">
-        <v>31.82016846817308</v>
+        <v>31.04908220229241</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5401684681730785</v>
+        <v>-0.2309177977075869</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2917819740084501</v>
+        <v>0.05332302929812203</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.38</v>
       </c>
       <c r="C20" t="n">
-        <v>31.52701370395522</v>
+        <v>30.83156346787992</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1470137039552171</v>
+        <v>-0.5484365321200748</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02161302915063221</v>
+        <v>0.3007826297638939</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.58</v>
       </c>
       <c r="C21" t="n">
-        <v>31.88891343994345</v>
+        <v>31.05406723183888</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3089134399434563</v>
+        <v>-0.5259327681611232</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09542751337769939</v>
+        <v>0.2766052766256218</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.65</v>
       </c>
       <c r="C22" t="n">
-        <v>31.84383637016819</v>
+        <v>31.59665854667251</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1938363701681887</v>
+        <v>-0.05334145332748363</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03757253839997906</v>
+        <v>0.002845310643088115</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.88</v>
       </c>
       <c r="C23" t="n">
-        <v>32.53161955139993</v>
+        <v>32.49295279257779</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6516195513999286</v>
+        <v>0.61295279257779</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4246080397666441</v>
+        <v>0.3757111259289113</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.28</v>
       </c>
       <c r="C24" t="n">
-        <v>32.44790752664425</v>
+        <v>32.51761548091525</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1679075266442496</v>
+        <v>0.2376154809152453</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02819293750378938</v>
+        <v>0.05646111677058331</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.45</v>
       </c>
       <c r="C25" t="n">
-        <v>32.56493877496955</v>
+        <v>32.75503165065629</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1149387749695521</v>
+        <v>0.3050316506562822</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01321092199150133</v>
+        <v>0.09304430790209621</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.85</v>
       </c>
       <c r="C26" t="n">
-        <v>32.83110401486227</v>
+        <v>32.96116689884062</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.01889598513773194</v>
+        <v>0.1111668988406223</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0003570582543253864</v>
+        <v>0.01235807939784114</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.9</v>
       </c>
       <c r="C27" t="n">
-        <v>32.98472376508364</v>
+        <v>33.02125648673261</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08472376508364476</v>
+        <v>0.1212564867326122</v>
       </c>
       <c r="E27" t="n">
-        <v>0.007178116369948624</v>
+        <v>0.01470313557473617</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>33.1</v>
       </c>
       <c r="C28" t="n">
-        <v>33.06027237251001</v>
+        <v>33.17862983298771</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.03972762748999514</v>
+        <v>0.07862983298770843</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001578284385983818</v>
+        <v>0.00618265063567492</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>33.4</v>
       </c>
       <c r="C29" t="n">
-        <v>33.94366062112429</v>
+        <v>33.54432577702764</v>
       </c>
       <c r="D29" t="n">
-        <v>0.543660621124296</v>
+        <v>0.144325777027646</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2955668709612553</v>
+        <v>0.0208299299146338</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>33.7</v>
       </c>
       <c r="C30" t="n">
-        <v>33.88600048284398</v>
+        <v>33.59484823058081</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1860004828439799</v>
+        <v>-0.1051517694191944</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03459617961819365</v>
+        <v>0.01105689461198742</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>34.1</v>
       </c>
       <c r="C31" t="n">
-        <v>34.03856700696136</v>
+        <v>33.6974953360889</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.06143299303864325</v>
+        <v>-0.4025046639111025</v>
       </c>
       <c r="E31" t="n">
-        <v>0.00377401263368599</v>
+        <v>0.1620100044701896</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>34.4</v>
       </c>
       <c r="C32" t="n">
-        <v>33.89030278293831</v>
+        <v>34.2781710818468</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5096972170616922</v>
+        <v>-0.1218289181531986</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2597912530804338</v>
+        <v>0.01484228529837877</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>34.9</v>
       </c>
       <c r="C33" t="n">
-        <v>34.49641451513467</v>
+        <v>34.59026156137988</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.4035854848653315</v>
+        <v>-0.3097384386201156</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1628812435939847</v>
+        <v>0.09593790035882714</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>35.3</v>
       </c>
       <c r="C34" t="n">
-        <v>35.58994005158812</v>
+        <v>35.69277273257615</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2899400515881254</v>
+        <v>0.3927727325761481</v>
       </c>
       <c r="E34" t="n">
-        <v>0.08406523351492483</v>
+        <v>0.1542704194553343</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>35.7</v>
       </c>
       <c r="C35" t="n">
-        <v>36.00345176899923</v>
+        <v>35.95596127809328</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3034517689992313</v>
+        <v>0.2559612780932738</v>
       </c>
       <c r="E35" t="n">
-        <v>0.09208297610876284</v>
+        <v>0.06551617588314226</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>36.3</v>
       </c>
       <c r="C36" t="n">
-        <v>36.22850760022378</v>
+        <v>36.34356418676805</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.07149239977621846</v>
+        <v>0.04356418676805163</v>
       </c>
       <c r="E36" t="n">
-        <v>0.005111163225762641</v>
+        <v>0.001897838368761684</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>36.8</v>
       </c>
       <c r="C37" t="n">
-        <v>37.13218751709188</v>
+        <v>36.87894717070319</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3321875170918815</v>
+        <v>0.07894717070319501</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1103485465116691</v>
+        <v>0.006232655762039413</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>37.3</v>
       </c>
       <c r="C38" t="n">
-        <v>37.1886072001539</v>
+        <v>37.02797098788045</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1113927998460937</v>
+        <v>-0.2720290121195461</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0124083558575519</v>
+        <v>0.07399978343473616</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>37.9</v>
       </c>
       <c r="C39" t="n">
-        <v>38.07902063115112</v>
+        <v>37.90215637364533</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1790206311511255</v>
+        <v>0.002156373645327392</v>
       </c>
       <c r="E39" t="n">
-        <v>0.03204838637774734</v>
+        <v>4.649947298262544e-06</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>38.5</v>
       </c>
       <c r="C40" t="n">
-        <v>38.68052565090631</v>
+        <v>38.58213526225354</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1805256509063113</v>
+        <v>0.08213526225353718</v>
       </c>
       <c r="E40" t="n">
-        <v>0.03258951063514739</v>
+        <v>0.006746201305457329</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>38.9</v>
       </c>
       <c r="C41" t="n">
-        <v>39.05890000262099</v>
+        <v>39.10436487970355</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1589000026209959</v>
+        <v>0.2043648797035473</v>
       </c>
       <c r="E41" t="n">
-        <v>0.02524921083295251</v>
+        <v>0.04176500405624537</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>39.4</v>
       </c>
       <c r="C42" t="n">
-        <v>39.46814730780111</v>
+        <v>39.423575650698</v>
       </c>
       <c r="D42" t="n">
-        <v>0.06814730780111233</v>
+        <v>0.02357565069799961</v>
       </c>
       <c r="E42" t="n">
-        <v>0.004644055560539546</v>
+        <v>0.0005558113058340893</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>39.9</v>
       </c>
       <c r="C43" t="n">
-        <v>39.71557728641135</v>
+        <v>39.69720863308636</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1844227135886527</v>
+        <v>-0.2027913669136368</v>
       </c>
       <c r="E43" t="n">
-        <v>0.03401173728740223</v>
+        <v>0.04112433849470125</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>40.1</v>
       </c>
       <c r="C44" t="n">
-        <v>39.75171229721425</v>
+        <v>39.75404246321752</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.348287702785754</v>
+        <v>-0.3459575367824783</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1213043239117778</v>
+        <v>0.1196866172565998</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>40.6</v>
       </c>
       <c r="C45" t="n">
-        <v>39.88865494367155</v>
+        <v>39.89197518924603</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.7113450563284474</v>
+        <v>-0.7080248107539688</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5060117891629219</v>
+        <v>0.5012991326431934</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>40.9</v>
       </c>
       <c r="C46" t="n">
-        <v>40.17636941192848</v>
+        <v>40.18348844285919</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.7236305880715221</v>
+        <v>-0.7165115571408123</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5236412279927369</v>
+        <v>0.5133888115163515</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>41.2</v>
       </c>
       <c r="C47" t="n">
-        <v>41.00493381187577</v>
+        <v>41.19773897167246</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1950661881242368</v>
+        <v>-0.002261028327538384</v>
       </c>
       <c r="E47" t="n">
-        <v>0.03805081774932015</v>
+        <v>5.11224909793102e-06</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>41.5</v>
       </c>
       <c r="C48" t="n">
-        <v>41.2232895644484</v>
+        <v>41.27961779414809</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2767104355515997</v>
+        <v>-0.2203822058519123</v>
       </c>
       <c r="E48" t="n">
-        <v>0.07656866514315601</v>
+        <v>0.04856831665615463</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>41.8</v>
       </c>
       <c r="C49" t="n">
-        <v>41.83429001822083</v>
+        <v>41.72409164356247</v>
       </c>
       <c r="D49" t="n">
-        <v>0.03429001822083677</v>
+        <v>-0.07590835643753024</v>
       </c>
       <c r="E49" t="n">
-        <v>0.001175805349585318</v>
+        <v>0.00576207857704714</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>42.2</v>
       </c>
       <c r="C50" t="n">
-        <v>42.2899883177875</v>
+        <v>42.39997101360544</v>
       </c>
       <c r="D50" t="n">
-        <v>0.08998831778749405</v>
+        <v>0.1999710136054347</v>
       </c>
       <c r="E50" t="n">
-        <v>0.008097897338223019</v>
+        <v>0.03998840628238494</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>42.7</v>
       </c>
       <c r="C51" t="n">
-        <v>43.42184316379691</v>
+        <v>43.53406211122057</v>
       </c>
       <c r="D51" t="n">
-        <v>0.7218431637969118</v>
+        <v>0.8340621112205682</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5210575531203353</v>
+        <v>0.6956596053737114</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.6918761771196742</v>
+        <v>-1.908077084219183</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>6.625964181312612</v>
+        <v>4.310722764377764</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.1325192836262522</v>
+        <v>0.08621445528755528</v>
       </c>
     </row>
   </sheetData>

--- a/partial/sliding_window_results_window_7.xlsx
+++ b/partial/sliding_window_results_window_7.xlsx
@@ -463,13 +463,13 @@
         <v>29.75</v>
       </c>
       <c r="C2" t="n">
-        <v>29.58759074234123</v>
+        <v>29.50524195390847</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1624092576587692</v>
+        <v>-0.2447580460915333</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02637676697327249</v>
+        <v>0.05990650112654514</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.84</v>
       </c>
       <c r="C3" t="n">
-        <v>30.18283030166088</v>
+        <v>30.0212017911905</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3428303016608787</v>
+        <v>0.181201791190496</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1175326157368891</v>
+        <v>0.0328340891306441</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.81</v>
       </c>
       <c r="C4" t="n">
-        <v>30.05240729647354</v>
+        <v>29.89889315594468</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2424072964735444</v>
+        <v>0.08889315594468172</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05876129738361286</v>
+        <v>0.007901993173805504</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.92</v>
       </c>
       <c r="C5" t="n">
-        <v>29.8008296316535</v>
+        <v>29.87536471620552</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1191703683464986</v>
+        <v>-0.04463528379448078</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01420157669184016</v>
+        <v>0.001992308559413839</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.98</v>
       </c>
       <c r="C6" t="n">
-        <v>29.81086508372359</v>
+        <v>29.67313537523131</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1691349162764055</v>
+        <v>-0.3068646247686893</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02860661990382671</v>
+        <v>0.09416589793442845</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.04</v>
       </c>
       <c r="C7" t="n">
-        <v>29.8588191652655</v>
+        <v>29.91896590726491</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1811808347345014</v>
+        <v>-0.1210340927350906</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03282649487509071</v>
+        <v>0.01464925160420651</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.21</v>
       </c>
       <c r="C8" t="n">
-        <v>29.96757500962112</v>
+        <v>29.90278486671723</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2424249903788791</v>
+        <v>-0.3072151332827744</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05876987596019963</v>
+        <v>0.09438113811795283</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.22</v>
       </c>
       <c r="C9" t="n">
-        <v>30.10526514425146</v>
+        <v>30.11958237044995</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1147348557485373</v>
+        <v>-0.1004176295500478</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01316408712363765</v>
+        <v>0.01008370032445064</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.38</v>
       </c>
       <c r="C10" t="n">
-        <v>30.16667345311208</v>
+        <v>30.24072255231465</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2133265468879237</v>
+        <v>-0.1392774476853447</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04550821560712553</v>
+        <v>0.01939820743374392</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.44</v>
       </c>
       <c r="C11" t="n">
-        <v>30.45523101141733</v>
+        <v>30.62996639351978</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01523101141732397</v>
+        <v>0.1899663935197822</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0002319837087946531</v>
+        <v>0.03608723066691274</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.48</v>
       </c>
       <c r="C12" t="n">
-        <v>30.47076606092922</v>
+        <v>30.41146774946451</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.009233939070778518</v>
+        <v>-0.06853225053549394</v>
       </c>
       <c r="E12" t="n">
-        <v>8.526563076285005e-05</v>
+        <v>0.00469666936345971</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.69</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43801446389514</v>
+        <v>30.43975427866008</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2519855361048577</v>
+        <v>-0.2502457213399261</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06349671040605256</v>
+        <v>0.06262292104893993</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.75</v>
       </c>
       <c r="C14" t="n">
-        <v>30.69975840814894</v>
+        <v>30.61975620763032</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.05024159185105859</v>
+        <v>-0.1302437923696793</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002524217551728357</v>
+        <v>0.01696344545083614</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.94</v>
       </c>
       <c r="C15" t="n">
-        <v>30.82994133128413</v>
+        <v>30.61960225086347</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1100586687158724</v>
+        <v>-0.3203977491365286</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01211291055951016</v>
+        <v>0.1026547176517539</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.95</v>
       </c>
       <c r="C16" t="n">
-        <v>30.96543978898074</v>
+        <v>30.7038594238387</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01543978898073917</v>
+        <v>-0.2461405761612987</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0002383870837697546</v>
+        <v>0.06058518323301609</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.02</v>
       </c>
       <c r="C17" t="n">
-        <v>31.14081628343929</v>
+        <v>31.00965791309393</v>
       </c>
       <c r="D17" t="n">
-        <v>0.120816283439293</v>
+        <v>-0.01034208690606775</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01459657434408357</v>
+        <v>0.000106958761572658</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.12</v>
       </c>
       <c r="C18" t="n">
-        <v>31.21232837632543</v>
+        <v>31.24066220122269</v>
       </c>
       <c r="D18" t="n">
-        <v>0.09232837632543323</v>
+        <v>0.1206622012226894</v>
       </c>
       <c r="E18" t="n">
-        <v>0.008524529074890819</v>
+        <v>0.0145593668039048</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.28</v>
       </c>
       <c r="C19" t="n">
-        <v>31.04908220229241</v>
+        <v>31.32077363989951</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2309177977075869</v>
+        <v>0.04077363989951266</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05332302929812203</v>
+        <v>0.001662489710655131</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.38</v>
       </c>
       <c r="C20" t="n">
-        <v>30.83156346787992</v>
+        <v>31.25411974418392</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5484365321200748</v>
+        <v>-0.1258802558160745</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3007826297638939</v>
+        <v>0.01584583880432037</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.58</v>
       </c>
       <c r="C21" t="n">
-        <v>31.05406723183888</v>
+        <v>31.54109299702632</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5259327681611232</v>
+        <v>-0.03890700297367999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2766052766256218</v>
+        <v>0.001513754880393944</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.65</v>
       </c>
       <c r="C22" t="n">
-        <v>31.59665854667251</v>
+        <v>31.55163784463415</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.05334145332748363</v>
+        <v>-0.09836215536584803</v>
       </c>
       <c r="E22" t="n">
-        <v>0.002845310643088115</v>
+        <v>0.009675113608215226</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.88</v>
       </c>
       <c r="C23" t="n">
-        <v>32.49295279257779</v>
+        <v>32.14709336041251</v>
       </c>
       <c r="D23" t="n">
-        <v>0.61295279257779</v>
+        <v>0.2670933604125061</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3757111259289113</v>
+        <v>0.07133886317644487</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.28</v>
       </c>
       <c r="C24" t="n">
-        <v>32.51761548091525</v>
+        <v>31.99691271959346</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2376154809152453</v>
+        <v>-0.2830872804065407</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05646111677058331</v>
+        <v>0.08013840832797142</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.45</v>
       </c>
       <c r="C25" t="n">
-        <v>32.75503165065629</v>
+        <v>32.24545019351771</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3050316506562822</v>
+        <v>-0.2045498064822908</v>
       </c>
       <c r="E25" t="n">
-        <v>0.09304430790209621</v>
+        <v>0.04184062333194263</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.85</v>
       </c>
       <c r="C26" t="n">
-        <v>32.96116689884062</v>
+        <v>32.97962897731193</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1111668988406223</v>
+        <v>0.1296289773119312</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01235807939784114</v>
+        <v>0.01680367175893718</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.9</v>
       </c>
       <c r="C27" t="n">
-        <v>33.02125648673261</v>
+        <v>33.14337581838996</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1212564867326122</v>
+        <v>0.2433758183899641</v>
       </c>
       <c r="E27" t="n">
-        <v>0.01470313557473617</v>
+        <v>0.05923178897698481</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>33.1</v>
       </c>
       <c r="C28" t="n">
-        <v>33.17862983298771</v>
+        <v>32.99558161539225</v>
       </c>
       <c r="D28" t="n">
-        <v>0.07862983298770843</v>
+        <v>-0.1044183846077473</v>
       </c>
       <c r="E28" t="n">
-        <v>0.00618265063567492</v>
+        <v>0.01090319904409144</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>33.4</v>
       </c>
       <c r="C29" t="n">
-        <v>33.54432577702764</v>
+        <v>33.60766041837754</v>
       </c>
       <c r="D29" t="n">
-        <v>0.144325777027646</v>
+        <v>0.207660418377543</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0208299299146338</v>
+        <v>0.0431228493607362</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>33.7</v>
       </c>
       <c r="C30" t="n">
-        <v>33.59484823058081</v>
+        <v>33.48584081389718</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1051517694191944</v>
+        <v>-0.214159186102826</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01105689461198742</v>
+        <v>0.04586415699222487</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>34.1</v>
       </c>
       <c r="C31" t="n">
-        <v>33.6974953360889</v>
+        <v>33.70809200628906</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4025046639111025</v>
+        <v>-0.3919079937109373</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1620100044701896</v>
+        <v>0.1535918755345321</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>34.4</v>
       </c>
       <c r="C32" t="n">
-        <v>34.2781710818468</v>
+        <v>34.13892968569343</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1218289181531986</v>
+        <v>-0.261070314306572</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01484228529837877</v>
+        <v>0.06815770901213231</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>34.9</v>
       </c>
       <c r="C33" t="n">
-        <v>34.59026156137988</v>
+        <v>34.73935815344803</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3097384386201156</v>
+        <v>-0.1606418465519681</v>
       </c>
       <c r="E33" t="n">
-        <v>0.09593790035882714</v>
+        <v>0.02580580286362607</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>35.3</v>
       </c>
       <c r="C34" t="n">
-        <v>35.69277273257615</v>
+        <v>35.41080853303002</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3927727325761481</v>
+        <v>0.1108085330300241</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1542704194553343</v>
+        <v>0.01227853099226595</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>35.7</v>
       </c>
       <c r="C35" t="n">
-        <v>35.95596127809328</v>
+        <v>35.7241447652425</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2559612780932738</v>
+        <v>0.02414476524249665</v>
       </c>
       <c r="E35" t="n">
-        <v>0.06551617588314226</v>
+        <v>0.0005829696886152741</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>36.3</v>
       </c>
       <c r="C36" t="n">
-        <v>36.34356418676805</v>
+        <v>36.24502301674239</v>
       </c>
       <c r="D36" t="n">
-        <v>0.04356418676805163</v>
+        <v>-0.05497698325761036</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001897838368761684</v>
+        <v>0.00302246868810757</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>36.8</v>
       </c>
       <c r="C37" t="n">
-        <v>36.87894717070319</v>
+        <v>36.86842700779583</v>
       </c>
       <c r="D37" t="n">
-        <v>0.07894717070319501</v>
+        <v>0.06842700779583311</v>
       </c>
       <c r="E37" t="n">
-        <v>0.006232655762039413</v>
+        <v>0.004682255395891005</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>37.3</v>
       </c>
       <c r="C38" t="n">
-        <v>37.02797098788045</v>
+        <v>37.02732320137338</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2720290121195461</v>
+        <v>-0.2726767986266125</v>
       </c>
       <c r="E38" t="n">
-        <v>0.07399978343473616</v>
+        <v>0.0743526365092582</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>37.9</v>
       </c>
       <c r="C39" t="n">
-        <v>37.90215637364533</v>
+        <v>37.91810741213857</v>
       </c>
       <c r="D39" t="n">
-        <v>0.002156373645327392</v>
+        <v>0.01810741213857625</v>
       </c>
       <c r="E39" t="n">
-        <v>4.649947298262544e-06</v>
+        <v>0.0003278783743562585</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>38.5</v>
       </c>
       <c r="C40" t="n">
-        <v>38.58213526225354</v>
+        <v>38.61995400144163</v>
       </c>
       <c r="D40" t="n">
-        <v>0.08213526225353718</v>
+        <v>0.1199540014416343</v>
       </c>
       <c r="E40" t="n">
-        <v>0.006746201305457329</v>
+        <v>0.01438896246185959</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>38.9</v>
       </c>
       <c r="C41" t="n">
-        <v>39.10436487970355</v>
+        <v>38.95083313367998</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2043648797035473</v>
+        <v>0.05083313367997988</v>
       </c>
       <c r="E41" t="n">
-        <v>0.04176500405624537</v>
+        <v>0.002584007479726705</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>39.4</v>
       </c>
       <c r="C42" t="n">
-        <v>39.423575650698</v>
+        <v>39.29530644487652</v>
       </c>
       <c r="D42" t="n">
-        <v>0.02357565069799961</v>
+        <v>-0.1046935551234824</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0005558113058340893</v>
+        <v>0.01096074048439366</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>39.9</v>
       </c>
       <c r="C43" t="n">
-        <v>39.69720863308636</v>
+        <v>39.75593919924394</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2027913669136368</v>
+        <v>-0.1440608007560584</v>
       </c>
       <c r="E43" t="n">
-        <v>0.04112433849470125</v>
+        <v>0.02075351431447676</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>40.1</v>
       </c>
       <c r="C44" t="n">
-        <v>39.75404246321752</v>
+        <v>39.63239996626486</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3459575367824783</v>
+        <v>-0.4676000337351383</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1196866172565998</v>
+        <v>0.2186497915491024</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>40.6</v>
       </c>
       <c r="C45" t="n">
-        <v>39.89197518924603</v>
+        <v>39.7613299082574</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.7080248107539688</v>
+        <v>-0.8386700917425998</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5012991326431934</v>
+        <v>0.7033675227835408</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>40.9</v>
       </c>
       <c r="C46" t="n">
-        <v>40.18348844285919</v>
+        <v>40.05062232112454</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.7165115571408123</v>
+        <v>-0.849377678875463</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5133888115163515</v>
+        <v>0.7214424413718692</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>41.2</v>
       </c>
       <c r="C47" t="n">
-        <v>41.19773897167246</v>
+        <v>41.33949928714325</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.002261028327538384</v>
+        <v>0.1394992871432521</v>
       </c>
       <c r="E47" t="n">
-        <v>5.11224909793102e-06</v>
+        <v>0.0194600511134755</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>41.5</v>
       </c>
       <c r="C48" t="n">
-        <v>41.27961779414809</v>
+        <v>41.23524460465136</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2203822058519123</v>
+        <v>-0.2647553953486437</v>
       </c>
       <c r="E48" t="n">
-        <v>0.04856831665615463</v>
+        <v>0.07009541936621662</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>41.8</v>
       </c>
       <c r="C49" t="n">
-        <v>41.72409164356247</v>
+        <v>41.48815692063975</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.07590835643753024</v>
+        <v>-0.3118430793602514</v>
       </c>
       <c r="E49" t="n">
-        <v>0.00576207857704714</v>
+        <v>0.09724610614488402</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>42.2</v>
       </c>
       <c r="C50" t="n">
-        <v>42.39997101360544</v>
+        <v>42.34215086902086</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1999710136054347</v>
+        <v>0.1421508690208526</v>
       </c>
       <c r="E50" t="n">
-        <v>0.03998840628238494</v>
+        <v>0.0202068695633836</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>42.7</v>
       </c>
       <c r="C51" t="n">
-        <v>43.53406211122057</v>
+        <v>43.5692236932835</v>
       </c>
       <c r="D51" t="n">
-        <v>0.8340621112205682</v>
+        <v>0.8692236932835016</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6956596053737114</v>
+        <v>0.7555498289654108</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1.908077084219183</v>
+        <v>-4.469338618462043</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>4.310722764377764</v>
+        <v>4.029037721015629</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.08621445528755528</v>
+        <v>0.08058075442031258</v>
       </c>
     </row>
   </sheetData>
